--- a/tests/fixtures/real_template.xlsx
+++ b/tests/fixtures/real_template.xlsx
@@ -19,9 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>会議記録テンプレート</t>
+  </si>
+  <si>
+    <t>折り返して表示する長めの注記テキスト</t>
   </si>
 </sst>
 </file>
@@ -86,12 +89,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -131,7 +137,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="2476500"/>
+          <a:off x="0" y="2790825"/>
           <a:ext cx="3048000" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -544,13 +550,21 @@
     <row r="11" spans="1:6">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
+      <c r="C11">
+        <f>SUM(C3:C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f>C11*2</f>
+        <v>0</v>
+      </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="2"/>
+    <row r="12" spans="1:6" ht="40" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
